--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2023_biobio.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2023_biobio.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>8.722298285834063</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>9.496045940511255</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>11.70264839564337</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>13.48024975995548</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>8.291920853956714</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>8.758739527943703</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>7.597587986285426</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>8.628248214654111</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>8.864070490697951</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,9 +571,6 @@
       <c r="E11">
         <v>13.24044701419007</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,9 +590,6 @@
       <c r="E12">
         <v>7.568605929826333</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -647,9 +609,6 @@
       <c r="E13">
         <v>15.55896626096802</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -669,9 +628,6 @@
       <c r="E14">
         <v>8.712918286822058</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -691,9 +647,6 @@
       <c r="E15">
         <v>7.85633005841917</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -713,9 +666,6 @@
       <c r="E16">
         <v>6.369740305471905</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -735,9 +685,6 @@
       <c r="E17">
         <v>11.49575664954545</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -757,9 +704,6 @@
       <c r="E18">
         <v>13.92942601931335</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -779,9 +723,6 @@
       <c r="E19">
         <v>7.663946430853907</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -801,9 +742,6 @@
       <c r="E20">
         <v>16.13944761612525</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -823,9 +761,6 @@
       <c r="E21">
         <v>14.98041928081495</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -845,9 +780,6 @@
       <c r="E22">
         <v>9.323450405545298</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -867,9 +799,6 @@
       <c r="E23">
         <v>14.52444976972094</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -889,9 +818,6 @@
       <c r="E24">
         <v>10.62343867986819</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -911,9 +837,6 @@
       <c r="E25">
         <v>9.796066737438846</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -933,9 +856,6 @@
       <c r="E26">
         <v>11.93452515188982</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -955,9 +875,6 @@
       <c r="E27">
         <v>13.49085095514204</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -977,9 +894,6 @@
       <c r="E28">
         <v>16.89807703602875</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -999,9 +913,6 @@
       <c r="E29">
         <v>11.22801780275537</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1021,9 +932,6 @@
       <c r="E30">
         <v>18.26170217562029</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1043,9 +951,6 @@
       <c r="E31">
         <v>10.91912029108626</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1065,9 +970,6 @@
       <c r="E32">
         <v>26.06427603711512</v>
       </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1087,9 +989,6 @@
       <c r="E33">
         <v>11.59800644112516</v>
       </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1108,9 +1007,6 @@
       </c>
       <c r="E34">
         <v>18.33665448936146</v>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2023_biobio.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2023_biobio.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -480,7 +480,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Los Ángeles</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="B7">
@@ -499,513 +499,532 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Laja</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B8">
-        <v>393771.03</v>
+        <v>394373.09</v>
       </c>
       <c r="C8">
-        <v>365966.41</v>
+        <v>359508.78</v>
       </c>
       <c r="D8">
-        <v>27804.62000000005</v>
+        <v>34864.31</v>
       </c>
       <c r="E8">
-        <v>7.597587986285426</v>
+        <v>9.697763153378336</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nacimiento</t>
+          <t>Laja</t>
         </is>
       </c>
       <c r="B9">
-        <v>382335.38</v>
+        <v>393771.03</v>
       </c>
       <c r="C9">
-        <v>351966.81</v>
+        <v>365966.41</v>
       </c>
       <c r="D9">
-        <v>30368.57000000001</v>
+        <v>27804.62000000005</v>
       </c>
       <c r="E9">
-        <v>8.628248214654111</v>
+        <v>7.597587986285426</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coronel</t>
+          <t>Nacimiento</t>
         </is>
       </c>
       <c r="B10">
-        <v>370585.75</v>
+        <v>382335.38</v>
       </c>
       <c r="C10">
-        <v>340411.44</v>
+        <v>351966.81</v>
       </c>
       <c r="D10">
-        <v>30174.31</v>
+        <v>30368.57000000001</v>
       </c>
       <c r="E10">
-        <v>8.864070490697951</v>
+        <v>8.628248214654111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Penco</t>
+          <t>Coronel</t>
         </is>
       </c>
       <c r="B11">
-        <v>367178.22</v>
+        <v>370585.75</v>
       </c>
       <c r="C11">
-        <v>324246.53</v>
+        <v>340411.44</v>
       </c>
       <c r="D11">
-        <v>42931.68999999994</v>
+        <v>30174.31</v>
       </c>
       <c r="E11">
-        <v>13.24044701419007</v>
+        <v>8.864070490697951</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Arauco</t>
+          <t>Penco</t>
         </is>
       </c>
       <c r="B12">
-        <v>363443.06</v>
+        <v>367178.22</v>
       </c>
       <c r="C12">
-        <v>337870.94</v>
+        <v>324246.53</v>
       </c>
       <c r="D12">
-        <v>25572.12</v>
+        <v>42931.68999999994</v>
       </c>
       <c r="E12">
-        <v>7.568605929826333</v>
+        <v>13.24044701419007</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Negrete</t>
+          <t>Arauco</t>
         </is>
       </c>
       <c r="B13">
-        <v>357161.09</v>
+        <v>363443.06</v>
       </c>
       <c r="C13">
-        <v>309072.59</v>
+        <v>337870.94</v>
       </c>
       <c r="D13">
-        <v>48088.5</v>
+        <v>25572.12</v>
       </c>
       <c r="E13">
-        <v>15.55896626096802</v>
+        <v>7.568605929826333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
+          <t>Negrete</t>
         </is>
       </c>
       <c r="B14">
-        <v>348057.66</v>
+        <v>357161.09</v>
       </c>
       <c r="C14">
-        <v>320162.19</v>
+        <v>309072.59</v>
       </c>
       <c r="D14">
-        <v>27895.46999999997</v>
+        <v>48088.5</v>
       </c>
       <c r="E14">
-        <v>8.712918286822058</v>
+        <v>15.55896626096802</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cabrero</t>
+          <t>Curanilahue</t>
         </is>
       </c>
       <c r="B15">
-        <v>332227.06</v>
+        <v>348057.66</v>
       </c>
       <c r="C15">
-        <v>308027.41</v>
+        <v>320162.19</v>
       </c>
       <c r="D15">
-        <v>24199.65000000002</v>
+        <v>27895.46999999997</v>
       </c>
       <c r="E15">
-        <v>7.85633005841917</v>
+        <v>8.712918286822058</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>San Rosendo</t>
+          <t>Cabrero</t>
         </is>
       </c>
       <c r="B16">
-        <v>330768.94</v>
+        <v>332227.06</v>
       </c>
       <c r="C16">
-        <v>310961.5</v>
+        <v>308027.41</v>
       </c>
       <c r="D16">
-        <v>19807.44</v>
+        <v>24199.65000000002</v>
       </c>
       <c r="E16">
-        <v>6.369740305471905</v>
+        <v>7.85633005841917</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tomé</t>
+          <t>San Rosendo</t>
         </is>
       </c>
       <c r="B17">
-        <v>321767.31</v>
+        <v>330768.94</v>
       </c>
       <c r="C17">
-        <v>288591.53</v>
+        <v>310961.5</v>
       </c>
       <c r="D17">
-        <v>33175.77999999997</v>
+        <v>19807.44</v>
       </c>
       <c r="E17">
-        <v>11.49575664954545</v>
+        <v>6.369740305471905</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hualqui</t>
+          <t>Tomé</t>
         </is>
       </c>
       <c r="B18">
-        <v>321616.72</v>
+        <v>321767.31</v>
       </c>
       <c r="C18">
-        <v>282294.69</v>
+        <v>288591.53</v>
       </c>
       <c r="D18">
-        <v>39322.02999999997</v>
+        <v>33175.77999999997</v>
       </c>
       <c r="E18">
-        <v>13.92942601931335</v>
+        <v>11.49575664954545</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lota</t>
+          <t>Hualqui</t>
         </is>
       </c>
       <c r="B19">
-        <v>319155.03</v>
+        <v>321616.72</v>
       </c>
       <c r="C19">
-        <v>296436.31</v>
+        <v>282294.69</v>
       </c>
       <c r="D19">
-        <v>22718.72000000003</v>
+        <v>39322.02999999997</v>
       </c>
       <c r="E19">
-        <v>7.663946430853907</v>
+        <v>13.92942601931335</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Antuco</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="B20">
-        <v>310513.47</v>
+        <v>319155.03</v>
       </c>
       <c r="C20">
-        <v>267362.62</v>
+        <v>296436.31</v>
       </c>
       <c r="D20">
-        <v>43150.84999999998</v>
+        <v>22718.72000000003</v>
       </c>
       <c r="E20">
-        <v>16.13944761612525</v>
+        <v>7.663946430853907</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
+          <t>Antuco</t>
         </is>
       </c>
       <c r="B21">
-        <v>307341.12</v>
+        <v>310513.47</v>
       </c>
       <c r="C21">
-        <v>267298.66</v>
+        <v>267362.62</v>
       </c>
       <c r="D21">
-        <v>40042.46000000002</v>
+        <v>43150.84999999998</v>
       </c>
       <c r="E21">
-        <v>14.98041928081495</v>
+        <v>16.13944761612525</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tucapel</t>
+          <t>Santa Juana</t>
         </is>
       </c>
       <c r="B22">
-        <v>296985.56</v>
+        <v>307341.12</v>
       </c>
       <c r="C22">
-        <v>271657.69</v>
+        <v>267298.66</v>
       </c>
       <c r="D22">
-        <v>25327.87</v>
+        <v>40042.46000000002</v>
       </c>
       <c r="E22">
-        <v>9.323450405545298</v>
+        <v>14.98041928081495</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Tucapel</t>
         </is>
       </c>
       <c r="B23">
-        <v>290949.88</v>
+        <v>296985.56</v>
       </c>
       <c r="C23">
-        <v>254050.45</v>
+        <v>271657.69</v>
       </c>
       <c r="D23">
-        <v>36899.42999999999</v>
+        <v>25327.87</v>
       </c>
       <c r="E23">
-        <v>14.52444976972094</v>
+        <v>9.323450405545298</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Los Álamos</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="B24">
-        <v>282302.94</v>
+        <v>290949.88</v>
       </c>
       <c r="C24">
-        <v>255192.7</v>
+        <v>254050.45</v>
       </c>
       <c r="D24">
-        <v>27110.23999999999</v>
+        <v>36899.42999999999</v>
       </c>
       <c r="E24">
-        <v>10.62343867986819</v>
+        <v>14.52444976972094</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mulchén</t>
+          <t>Los Alamos</t>
         </is>
       </c>
       <c r="B25">
-        <v>282293</v>
+        <v>282302.94</v>
       </c>
       <c r="C25">
-        <v>257106.66</v>
+        <v>255192.7</v>
       </c>
       <c r="D25">
-        <v>25186.34</v>
+        <v>27110.23999999999</v>
       </c>
       <c r="E25">
-        <v>9.796066737438846</v>
+        <v>10.62343867986819</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quilleco</t>
+          <t>Mulchén</t>
         </is>
       </c>
       <c r="B26">
-        <v>272741.69</v>
+        <v>282293</v>
       </c>
       <c r="C26">
-        <v>243661.81</v>
+        <v>257106.66</v>
       </c>
       <c r="D26">
-        <v>29079.88</v>
+        <v>25186.34</v>
       </c>
       <c r="E26">
-        <v>11.93452515188982</v>
+        <v>9.796066737438846</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Quilleco</t>
         </is>
       </c>
       <c r="B27">
-        <v>265580.19</v>
+        <v>272741.69</v>
       </c>
       <c r="C27">
-        <v>234010.22</v>
+        <v>243661.81</v>
       </c>
       <c r="D27">
-        <v>31569.97</v>
+        <v>29079.88</v>
       </c>
       <c r="E27">
-        <v>13.49085095514204</v>
+        <v>11.93452515188982</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quilaco</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="B28">
-        <v>255748.97</v>
+        <v>265580.19</v>
       </c>
       <c r="C28">
-        <v>218779.45</v>
+        <v>234010.22</v>
       </c>
       <c r="D28">
-        <v>36969.51999999999</v>
+        <v>31569.97</v>
       </c>
       <c r="E28">
-        <v>16.89807703602875</v>
+        <v>13.49085095514204</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Yumbel</t>
+          <t>Quilaco</t>
         </is>
       </c>
       <c r="B29">
-        <v>245985.8</v>
+        <v>255748.97</v>
       </c>
       <c r="C29">
-        <v>221154.53</v>
+        <v>218779.45</v>
       </c>
       <c r="D29">
-        <v>24831.26999999999</v>
+        <v>36969.51999999999</v>
       </c>
       <c r="E29">
-        <v>11.22801780275537</v>
+        <v>16.89807703602875</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Contulmo</t>
+          <t>Yumbel</t>
         </is>
       </c>
       <c r="B30">
-        <v>241858.58</v>
+        <v>245985.8</v>
       </c>
       <c r="C30">
-        <v>204511.33</v>
+        <v>221154.53</v>
       </c>
       <c r="D30">
-        <v>37347.25</v>
+        <v>24831.26999999999</v>
       </c>
       <c r="E30">
-        <v>18.26170217562029</v>
+        <v>11.22801780275537</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cañete</t>
+          <t>Contulmo</t>
         </is>
       </c>
       <c r="B31">
-        <v>236898.75</v>
+        <v>241858.58</v>
       </c>
       <c r="C31">
-        <v>213577.92</v>
+        <v>204511.33</v>
       </c>
       <c r="D31">
-        <v>23320.82999999999</v>
+        <v>37347.25</v>
       </c>
       <c r="E31">
-        <v>10.91912029108626</v>
+        <v>18.26170217562029</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alto Biobío</t>
+          <t>Cañete</t>
         </is>
       </c>
       <c r="B32">
-        <v>229423.67</v>
+        <v>236898.75</v>
       </c>
       <c r="C32">
-        <v>181989.44</v>
+        <v>213577.92</v>
       </c>
       <c r="D32">
-        <v>47434.23000000001</v>
+        <v>23320.82999999999</v>
       </c>
       <c r="E32">
-        <v>26.06427603711512</v>
+        <v>10.91912029108626</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lebu</t>
+          <t>Alto Biobío</t>
         </is>
       </c>
       <c r="B33">
-        <v>222571.41</v>
+        <v>229423.67</v>
       </c>
       <c r="C33">
-        <v>199440.31</v>
+        <v>181989.44</v>
       </c>
       <c r="D33">
-        <v>23131.10000000001</v>
+        <v>47434.23000000001</v>
       </c>
       <c r="E33">
-        <v>11.59800644112516</v>
+        <v>26.06427603711512</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Lebu</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>222571.41</v>
+      </c>
+      <c r="C34">
+        <v>199440.31</v>
+      </c>
+      <c r="D34">
+        <v>23131.10000000001</v>
+      </c>
+      <c r="E34">
+        <v>11.59800644112516</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Tirúa</t>
         </is>
       </c>
-      <c r="B34">
+      <c r="B35">
         <v>197064.09</v>
       </c>
-      <c r="C34">
+      <c r="C35">
         <v>166528.36</v>
       </c>
-      <c r="D34">
+      <c r="D35">
         <v>30535.73000000001</v>
       </c>
-      <c r="E34">
+      <c r="E35">
         <v>18.33665448936146</v>
       </c>
     </row>
@@ -1184,7 +1203,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Los Álamos</t>
+          <t>Los Alamos</t>
         </is>
       </c>
       <c r="B17">
@@ -1194,7 +1213,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Los Ángeles</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="B18">

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2023_biobio.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2023_biobio.xlsx
@@ -1035,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1044,290 +1044,201 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alto Biobío</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>229423.67</v>
+          <t>Cañete</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Antuco</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>310513.47</v>
+          <t>Contulmo</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arauco</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>363443.06</v>
+          <t>Curanilahue</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cabrero</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>332227.06</v>
+          <t>Lebu</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cañete</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>236898.75</v>
+          <t>Los Alamos</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chiguayante</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>472513.44</v>
+          <t>Laja</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Concepción</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>494916.62</v>
+          <t>Los Angeles</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Contulmo</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>241858.58</v>
+          <t>Mulchén</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coronel</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>370585.75</v>
+          <t>Nacimiento</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>348057.66</v>
+          <t>Negrete</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>265580.19</v>
+          <t>Quilaco</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hualpén</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>417352.59</v>
+          <t>Quilleco</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hualqui</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>321616.72</v>
+          <t>San Rosendo</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Laja</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>393771.03</v>
+          <t>Tucapel</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lebu</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>222571.41</v>
+          <t>Chiguayante</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Los Alamos</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>282302.94</v>
+          <t>Concepción</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>396248.84</v>
+          <t>Coronel</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lota</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>319155.03</v>
+          <t>Florida</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mulchén</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>282293</v>
+          <t>Hualqui</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nacimiento</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>382335.38</v>
+          <t>Lota</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Negrete</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>357161.09</v>
+          <t>San Pedro de la Paz</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Penco</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>367178.22</v>
+          <t>Santa Juana</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Quilaco</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>255748.97</v>
+          <t>Yumbel</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quilleco</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>272741.69</v>
+          <t>Cabrero</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>San Pedro de la Paz</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>528966.5</v>
+          <t>Antuco</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>San Rosendo</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>330768.94</v>
+          <t>Alto Biobío</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>290949.88</v>
+          <t>Tirúa</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>307341.12</v>
+          <t>Hualpén</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1336,18 +1247,12 @@
           <t>Talcahuano</t>
         </is>
       </c>
-      <c r="B30">
-        <v>411720.88</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tirúa</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>197064.09</v>
+          <t>Penco</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1356,28 +1261,19 @@
           <t>Tomé</t>
         </is>
       </c>
-      <c r="B32">
-        <v>321767.31</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tucapel</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>296985.56</v>
+          <t>Arauco</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Yumbel</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>245985.8</v>
+          <t>Santa Bárbara</t>
+        </is>
       </c>
     </row>
   </sheetData>
